--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.88444</v>
+        <v>16.92684</v>
       </c>
       <c r="D2" t="n">
-        <v>16.60711</v>
+        <v>16.63402</v>
       </c>
       <c r="E2" t="n">
-        <v>16.50861</v>
+        <v>16.8019</v>
       </c>
       <c r="F2" t="n">
-        <v>42.56851</v>
+        <v>42.88017</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05176</v>
+        <v>0.05047</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7959</v>
+        <v>1.80454</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.58586</v>
+        <v>16.76392</v>
       </c>
       <c r="D3" t="n">
-        <v>16.49636</v>
+        <v>16.37102</v>
       </c>
       <c r="E3" t="n">
-        <v>16.6965</v>
+        <v>16.7211</v>
       </c>
       <c r="F3" t="n">
-        <v>42.04073</v>
+        <v>41.6966</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05063</v>
+        <v>0.05064</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84001</v>
+        <v>1.87524</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.0715</v>
+        <v>16.81787</v>
       </c>
       <c r="D4" t="n">
-        <v>16.99604</v>
+        <v>16.56223</v>
       </c>
       <c r="E4" t="n">
-        <v>16.54752</v>
+        <v>16.6467</v>
       </c>
       <c r="F4" t="n">
-        <v>42.67548</v>
+        <v>42.66949</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0505</v>
+        <v>0.05062</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82208</v>
+        <v>1.82798</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.87124</v>
+        <v>16.6484</v>
       </c>
       <c r="D6" t="n">
-        <v>15.94766</v>
+        <v>16.11086</v>
       </c>
       <c r="E6" t="n">
-        <v>16.57195</v>
+        <v>16.20904</v>
       </c>
       <c r="F6" t="n">
-        <v>21.70641</v>
+        <v>22.05489</v>
       </c>
       <c r="G6" t="n">
-        <v>34.35863</v>
+        <v>33.78997</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.66865</v>
+        <v>16.54234</v>
       </c>
       <c r="D7" t="n">
-        <v>15.80852</v>
+        <v>15.55903</v>
       </c>
       <c r="E7" t="n">
-        <v>16.48303</v>
+        <v>16.44775</v>
       </c>
       <c r="F7" t="n">
-        <v>21.54606</v>
+        <v>21.47812</v>
       </c>
       <c r="G7" t="n">
-        <v>34.62478</v>
+        <v>34.5043</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.8329</v>
+        <v>16.62592</v>
       </c>
       <c r="D8" t="n">
-        <v>16.1056</v>
+        <v>16.36105</v>
       </c>
       <c r="E8" t="n">
-        <v>16.74916</v>
+        <v>16.56374</v>
       </c>
       <c r="F8" t="n">
-        <v>21.58104</v>
+        <v>21.90713</v>
       </c>
       <c r="G8" t="n">
-        <v>33.60518</v>
+        <v>33.66124</v>
       </c>
     </row>
   </sheetData>
